--- a/output/forecast_next_period.xlsx
+++ b/output/forecast_next_period.xlsx
@@ -65292,12 +65292,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Dec-24</t>
+          <t>Dec-25</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Dec-25</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">

--- a/output/forecast_next_period.xlsx
+++ b/output/forecast_next_period.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="forecast" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="model_comparison" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="model_weights" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -65495,4 +65496,110 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>weight_%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>intercept</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-20.98727058806068</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rel_return_1_pct</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11.69990652206314</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rel_vol_pct</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7.592610848592578</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>size_rank_chg_pct</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7.43381565623787</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>share_chg_2_pct</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-3.818061208866808</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>share_chg_1_pct</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.414525837256245</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>size_rank_pct</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-2.471204509518618</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rel_return_2_pct</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1775806467026379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>